--- a/data/trans_dic/P16A08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,47 +717,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,93</t>
+          <t>1,22; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,06</t>
+          <t>1,81; 4,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,08</t>
+          <t>1,69; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,41</t>
+          <t>0,86; 3,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,8</t>
+          <t>2,71; 4,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,65</t>
+          <t>3,47; 5,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,53</t>
+          <t>2,84; 5,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,64</t>
+          <t>2,54; 4,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,76</t>
+          <t>2,29; 3,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,45</t>
+          <t>2,67; 4,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,68</t>
+          <t>2,08; 3,64</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,05</t>
+          <t>1,49; 3,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,2</t>
+          <t>2,57; 4,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,63</t>
+          <t>2,18; 3,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,97</t>
+          <t>2,42; 4,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,13</t>
+          <t>3,23; 5,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,07</t>
+          <t>4,79; 7,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,79</t>
+          <t>4,65; 6,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 18,43</t>
+          <t>4,01; 19,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,77</t>
+          <t>2,46; 3,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,23</t>
+          <t>3,91; 5,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,9</t>
+          <t>3,54; 4,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,31</t>
+          <t>3,77; 11,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,1</t>
+          <t>2,58; 6,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,86</t>
+          <t>3,27; 7,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,73</t>
+          <t>2,71; 6,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,65</t>
+          <t>1,44; 4,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,37</t>
+          <t>2,45; 6,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,85</t>
+          <t>4,95; 10,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,49</t>
+          <t>5,0; 9,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,62</t>
+          <t>4,25; 7,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,47</t>
+          <t>2,91; 5,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,13</t>
+          <t>4,65; 8,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,4</t>
+          <t>4,45; 7,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,38</t>
+          <t>3,2; 5,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,01</t>
+          <t>1,86; 2,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,13</t>
+          <t>2,79; 4,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,75</t>
+          <t>2,57; 3,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,08</t>
+          <t>2,42; 4,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,59</t>
+          <t>3,27; 4,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 6,35</t>
+          <t>4,75; 6,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,08</t>
+          <t>4,6; 6,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 14,11</t>
+          <t>4,2; 13,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,64</t>
+          <t>2,74; 3,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 4,98</t>
+          <t>4,01; 5,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 4,75</t>
+          <t>3,79; 4,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,69</t>
+          <t>3,67; 8,09</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12414; 30214</t>
+          <t>12542; 31264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16841; 39465</t>
+          <t>17625; 40329</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12670; 30742</t>
+          <t>12777; 30401</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4372; 17492</t>
+          <t>4435; 17567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35903; 63146</t>
+          <t>35649; 62718</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45163; 75255</t>
+          <t>46307; 78178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27881; 55033</t>
+          <t>28258; 55315</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19940; 34846</t>
+          <t>19127; 34538</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54623; 88142</t>
+          <t>53638; 85613</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69203; 107236</t>
+          <t>69067; 107091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46475; 77815</t>
+          <t>46669; 75876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26979; 46578</t>
+          <t>26373; 46069</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25074; 51692</t>
+          <t>25289; 51036</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50243; 82411</t>
+          <t>50289; 85100</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46100; 75345</t>
+          <t>45365; 75646</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59405; 113852</t>
+          <t>55329; 109974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51709; 81470</t>
+          <t>51316; 82223</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82636; 123773</t>
+          <t>83932; 123536</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92191; 134930</t>
+          <t>92531; 133743</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89688; 412217</t>
+          <t>89780; 425020</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82738; 123743</t>
+          <t>80607; 120718</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142001; 193965</t>
+          <t>145203; 196100</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145173; 199200</t>
+          <t>143775; 197061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>172836; 512200</t>
+          <t>170803; 534794</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14253; 33658</t>
+          <t>14247; 34867</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15449; 37756</t>
+          <t>15694; 37135</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16052; 36809</t>
+          <t>14836; 35815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9750; 30049</t>
+          <t>9330; 30007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10995; 30347</t>
+          <t>11677; 30567</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22271; 45060</t>
+          <t>22651; 46432</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27346; 52132</t>
+          <t>27430; 52597</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28012; 50327</t>
+          <t>28046; 50777</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30212; 56222</t>
+          <t>29886; 56329</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42830; 76275</t>
+          <t>43591; 75683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48780; 81092</t>
+          <t>48767; 81759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40805; 70363</t>
+          <t>41845; 70396</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61545; 98468</t>
+          <t>61076; 96429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94888; 140813</t>
+          <t>95331; 139389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85621; 126533</t>
+          <t>86687; 127696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82984; 140785</t>
+          <t>83500; 141787</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110742; 154949</t>
+          <t>110391; 157218</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167543; 224798</t>
+          <t>168086; 225297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>159880; 214817</t>
+          <t>162585; 215981</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>155608; 514848</t>
+          <t>153177; 492338</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180513; 242450</t>
+          <t>182254; 242954</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>276243; 346025</t>
+          <t>278900; 348451</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>261469; 327985</t>
+          <t>261876; 330370</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>258065; 617058</t>
+          <t>260606; 574267</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,03</t>
+          <t>1,22; 2,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,15</t>
+          <t>1,82; 4,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,03</t>
+          <t>1,71; 4,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,42</t>
+          <t>0,77; 3,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,77</t>
+          <t>2,77; 4,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,87</t>
+          <t>3,3; 5,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,56</t>
+          <t>2,85; 5,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,59</t>
+          <t>2,77; 4,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,65</t>
+          <t>2,32; 3,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,65</t>
+          <t>2,99; 4,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,34</t>
+          <t>2,63; 4,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,64</t>
+          <t>2,19; 3,7</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,02</t>
+          <t>1,5; 3,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,34</t>
+          <t>2,61; 4,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,64</t>
+          <t>2,15; 3,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,8</t>
+          <t>3,03; 5,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,18</t>
+          <t>3,19; 5,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,06</t>
+          <t>4,79; 7,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,73</t>
+          <t>4,6; 6,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 19,0</t>
+          <t>4,14; 5,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,68</t>
+          <t>2,52; 3,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 5,28</t>
+          <t>3,85; 5,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,85</t>
+          <t>3,62; 4,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,81</t>
+          <t>3,85; 5,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,32</t>
+          <t>2,58; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,73</t>
+          <t>3,23; 8,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,55</t>
+          <t>2,94; 6,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,64</t>
+          <t>1,77; 4,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,42</t>
+          <t>2,45; 6,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,15</t>
+          <t>5,01; 10,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,58</t>
+          <t>5,09; 9,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,69</t>
+          <t>4,55; 7,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,48</t>
+          <t>2,83; 5,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,07</t>
+          <t>4,76; 8,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,46</t>
+          <t>4,47; 7,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,39</t>
+          <t>3,55; 5,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,94</t>
+          <t>1,89; 2,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,09</t>
+          <t>2,78; 4,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,78</t>
+          <t>2,53; 3,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,11</t>
+          <t>2,74; 4,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,65</t>
+          <t>3,32; 4,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,36</t>
+          <t>4,75; 6,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,11</t>
+          <t>4,7; 6,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 13,49</t>
+          <t>4,37; 5,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,65</t>
+          <t>2,73; 3,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,01</t>
+          <t>3,99; 5,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,78</t>
+          <t>3,75; 4,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,09</t>
+          <t>3,73; 4,65</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>30664</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>40123</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12542; 31264</t>
+          <t>12588; 30660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17625; 40329</t>
+          <t>17698; 39721</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12777; 30401</t>
+          <t>12910; 30731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4435; 17567</t>
+          <t>4443; 17689</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35649; 62718</t>
+          <t>36368; 62995</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46307; 78178</t>
+          <t>44042; 74848</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28258; 55315</t>
+          <t>28390; 55884</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19127; 34538</t>
+          <t>22715; 39244</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53638; 85613</t>
+          <t>54551; 85705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69067; 107091</t>
+          <t>68956; 107922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46669; 75876</t>
+          <t>45989; 76662</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26373; 46069</t>
+          <t>30538; 51683</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85028</t>
+          <t>86865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>166013</t>
+          <t>110533</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>251041</t>
+          <t>197397</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25289; 51036</t>
+          <t>25470; 50859</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50289; 85100</t>
+          <t>51178; 84053</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45365; 75646</t>
+          <t>44669; 78665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55329; 109974</t>
+          <t>67656; 112265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51316; 82223</t>
+          <t>50632; 82106</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83932; 123536</t>
+          <t>83941; 124743</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92531; 133743</t>
+          <t>91470; 132586</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89780; 425020</t>
+          <t>89899; 129359</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80607; 120718</t>
+          <t>82545; 122111</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>145203; 196100</t>
+          <t>142987; 195381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143775; 197061</t>
+          <t>147252; 197346</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>170803; 534794</t>
+          <t>169477; 225910</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>43725</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54504</t>
+          <t>65065</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14247; 34867</t>
+          <t>14226; 33047</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15694; 37135</t>
+          <t>15518; 39076</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14836; 35815</t>
+          <t>16085; 37630</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9330; 30007</t>
+          <t>12571; 32465</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11677; 30567</t>
+          <t>11692; 31033</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22651; 46432</t>
+          <t>22932; 46264</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27430; 52597</t>
+          <t>27977; 53682</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28046; 50777</t>
+          <t>33461; 57908</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29886; 56329</t>
+          <t>29123; 55277</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43591; 75683</t>
+          <t>44607; 77468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48767; 81759</t>
+          <t>48968; 82516</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41845; 70396</t>
+          <t>51329; 86075</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110918</t>
+          <t>117664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>340600</t>
+          <t>302586</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61076; 96429</t>
+          <t>61806; 97361</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95331; 139389</t>
+          <t>94776; 139798</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86687; 127696</t>
+          <t>85477; 127005</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83500; 141787</t>
+          <t>96599; 145640</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110391; 157218</t>
+          <t>112128; 156802</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>168086; 225297</t>
+          <t>168124; 223023</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>162585; 215981</t>
+          <t>165838; 222815</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>153177; 492338</t>
+          <t>162735; 210087</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182254; 242954</t>
+          <t>181916; 238183</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>278900; 348451</t>
+          <t>277482; 350660</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>261876; 330370</t>
+          <t>258822; 328197</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>260606; 574267</t>
+          <t>270447; 337098</t>
         </is>
       </c>
     </row>
